--- a/fix-errors/ig/FRCustodianLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRCustodianLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-header-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-header-document|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-custodian</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-custodian|0.1.0</t>
   </si>
   <si>
     <t>FRLMHeaderDocument.custodian</t>
@@ -123,7 +123,7 @@
     <t>custodian.assignedCustodian.representedCustodianOrganization</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>Composition.custodian</t>
